--- a/krm/static/files/import_companies_en.xlsx
+++ b/krm/static/files/import_companies_en.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bienvenidosaez/Bitbucket/krm-kpmg/krm/static/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bienvenidosaez/Bitbucket/krc-kpmg/krc/static/assets/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A1CFC-9804-7D4B-AB60-0855329C0F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED4B117-4E17-B346-BC68-DC774E1BF1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="23880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="24100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="508">
   <si>
     <t>VAT</t>
   </si>
@@ -1553,6 +1553,9 @@
     <t>ADDRESS</t>
   </si>
   <si>
+    <t>CICY</t>
+  </si>
+  <si>
     <t>POSTAL CODE</t>
   </si>
   <si>
@@ -1565,7 +1568,7 @@
     <t>CODE</t>
   </si>
   <si>
-    <t>CITY</t>
+    <t>REF</t>
   </si>
 </sst>
 </file>
@@ -2065,41 +2068,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="B1" s="10"/>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1"/>
+      <c r="B1" s="9" t="s">
+        <v>505</v>
+      </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>502</v>
@@ -2108,20 +2113,23 @@
         <v>503</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D4" s="3"/>
-      <c r="G4" s="3"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -2130,9 +2138,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1D5701C4-C796-2344-99F1-75AE5206539D}">
           <x14:formula1>
-            <xm:f>'Country Codes'!A2:A250</xm:f>
+            <xm:f>'Country Codes'!B2:B250</xm:f>
           </x14:formula1>
-          <xm:sqref>F3:F820</xm:sqref>
+          <xm:sqref>G3:G820</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2151,10 +2159,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.25">
@@ -2557,7 +2565,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>103</v>
       </c>

--- a/krm/static/files/import_companies_en.xlsx
+++ b/krm/static/files/import_companies_en.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bienvenidosaez/Bitbucket/krc-kpmg/krc/static/assets/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bienvenidosaez/Bitbucket/krm-kpmg/krm/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED4B117-4E17-B346-BC68-DC774E1BF1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F28C36F-EB2B-7544-B2F8-F97B601A72E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="24100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="41600" windowHeight="25520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="510">
   <si>
     <t>VAT</t>
   </si>
@@ -1569,6 +1569,12 @@
   </si>
   <si>
     <t>REF</t>
+  </si>
+  <si>
+    <t>COMPANIES IN SCOPE</t>
+  </si>
+  <si>
+    <t>TYPE</t>
   </si>
 </sst>
 </file>
@@ -2068,7 +2074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.1640625" style="2" customWidth="1"/>
@@ -2079,9 +2085,10 @@
     <col min="6" max="6" width="29.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="32.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1"/>
       <c r="B1" s="9" t="s">
         <v>505</v>
@@ -2092,8 +2099,10 @@
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1"/>
+      <c r="J1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>507</v>
       </c>
@@ -2118,12 +2127,18 @@
       <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E4" s="3"/>
       <c r="H4" s="3"/>
     </row>

--- a/krm/static/files/import_companies_en.xlsx
+++ b/krm/static/files/import_companies_en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bienvenidosaez/Bitbucket/krm-kpmg/krm/static/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicolasfernandorodri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F28C36F-EB2B-7544-B2F8-F97B601A72E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0611F973-7EDC-4BCE-9B03-8AE891EFAC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="41600" windowHeight="25520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="516">
   <si>
     <t>VAT</t>
   </si>
@@ -1553,9 +1553,6 @@
     <t>ADDRESS</t>
   </si>
   <si>
-    <t>CICY</t>
-  </si>
-  <si>
     <t>POSTAL CODE</t>
   </si>
   <si>
@@ -1575,6 +1572,27 @@
   </si>
   <si>
     <t>TYPE</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>A123456</t>
+  </si>
+  <si>
+    <t>TEST ADDRESS</t>
+  </si>
+  <si>
+    <t>01234</t>
+  </si>
+  <si>
+    <t>test@nomail.com</t>
+  </si>
+  <si>
+    <t>COMPANY</t>
+  </si>
+  <si>
+    <t>STATE</t>
   </si>
 </sst>
 </file>
@@ -1725,14 +1743,14 @@
     </xf>
   </cellXfs>
   <cellStyles count="9">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hipervínculo" xfId="7" builtinId="8"/>
-    <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2075,23 +2093,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="32.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1"/>
       <c r="B1" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2102,9 +2120,9 @@
       <c r="I1"/>
       <c r="J1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>500</v>
@@ -2116,29 +2134,57 @@
         <v>501</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E4" s="3"/>
       <c r="H4" s="3"/>
     </row>
@@ -2146,6 +2192,9 @@
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{418A89E0-4983-4AA2-9B80-6AD0FFC398BB}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
@@ -2166,21 +2215,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EEAAE1-F09A-E047-87B9-559B11FA38A3}">
   <dimension ref="A1:B250"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2188,7 +2237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
@@ -2196,7 +2245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -2204,7 +2253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
@@ -2212,7 +2261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2220,7 +2269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
@@ -2228,7 +2277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
@@ -2236,7 +2285,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
@@ -2244,7 +2293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -2252,7 +2301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>21</v>
       </c>
@@ -2260,7 +2309,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
@@ -2268,7 +2317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -2276,7 +2325,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
@@ -2284,7 +2333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
@@ -2292,7 +2341,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
@@ -2300,7 +2349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -2308,7 +2357,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>35</v>
       </c>
@@ -2316,7 +2365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>37</v>
       </c>
@@ -2324,7 +2373,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>39</v>
       </c>
@@ -2332,7 +2381,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
@@ -2340,7 +2389,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>43</v>
       </c>
@@ -2348,7 +2397,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>45</v>
       </c>
@@ -2356,7 +2405,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>47</v>
       </c>
@@ -2364,7 +2413,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
@@ -2372,7 +2421,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>51</v>
       </c>
@@ -2380,7 +2429,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>53</v>
       </c>
@@ -2388,7 +2437,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>55</v>
       </c>
@@ -2396,7 +2445,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>57</v>
       </c>
@@ -2404,7 +2453,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>59</v>
       </c>
@@ -2412,7 +2461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>61</v>
       </c>
@@ -2420,7 +2469,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>63</v>
       </c>
@@ -2428,7 +2477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>65</v>
       </c>
@@ -2436,7 +2485,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>67</v>
       </c>
@@ -2444,7 +2493,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>69</v>
       </c>
@@ -2452,7 +2501,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>71</v>
       </c>
@@ -2460,7 +2509,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>73</v>
       </c>
@@ -2468,7 +2517,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>75</v>
       </c>
@@ -2476,7 +2525,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>77</v>
       </c>
@@ -2484,7 +2533,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>79</v>
       </c>
@@ -2492,7 +2541,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>81</v>
       </c>
@@ -2500,7 +2549,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>83</v>
       </c>
@@ -2508,7 +2557,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>85</v>
       </c>
@@ -2516,7 +2565,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>87</v>
       </c>
@@ -2524,7 +2573,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>89</v>
       </c>
@@ -2532,7 +2581,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>91</v>
       </c>
@@ -2540,7 +2589,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>93</v>
       </c>
@@ -2548,7 +2597,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>95</v>
       </c>
@@ -2556,7 +2605,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>97</v>
       </c>
@@ -2564,7 +2613,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>99</v>
       </c>
@@ -2572,7 +2621,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>101</v>
       </c>
@@ -2580,7 +2629,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>103</v>
       </c>
@@ -2588,7 +2637,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>105</v>
       </c>
@@ -2596,7 +2645,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>107</v>
       </c>
@@ -2604,7 +2653,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>109</v>
       </c>
@@ -2612,7 +2661,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>111</v>
       </c>
@@ -2620,7 +2669,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>113</v>
       </c>
@@ -2628,7 +2677,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>115</v>
       </c>
@@ -2636,7 +2685,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>117</v>
       </c>
@@ -2644,7 +2693,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>119</v>
       </c>
@@ -2652,7 +2701,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>121</v>
       </c>
@@ -2660,7 +2709,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>123</v>
       </c>
@@ -2668,7 +2717,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>125</v>
       </c>
@@ -2676,7 +2725,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>127</v>
       </c>
@@ -2684,7 +2733,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>129</v>
       </c>
@@ -2692,7 +2741,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>131</v>
       </c>
@@ -2700,7 +2749,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>133</v>
       </c>
@@ -2708,7 +2757,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>135</v>
       </c>
@@ -2716,7 +2765,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>137</v>
       </c>
@@ -2724,7 +2773,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>139</v>
       </c>
@@ -2732,7 +2781,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>141</v>
       </c>
@@ -2740,7 +2789,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>143</v>
       </c>
@@ -2748,7 +2797,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>145</v>
       </c>
@@ -2756,7 +2805,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>147</v>
       </c>
@@ -2764,7 +2813,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>149</v>
       </c>
@@ -2772,7 +2821,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>151</v>
       </c>
@@ -2780,7 +2829,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>153</v>
       </c>
@@ -2788,7 +2837,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>155</v>
       </c>
@@ -2796,7 +2845,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>157</v>
       </c>
@@ -2804,7 +2853,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>159</v>
       </c>
@@ -2812,7 +2861,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>161</v>
       </c>
@@ -2820,7 +2869,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>163</v>
       </c>
@@ -2828,7 +2877,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>165</v>
       </c>
@@ -2836,7 +2885,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>167</v>
       </c>
@@ -2844,7 +2893,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>169</v>
       </c>
@@ -2852,7 +2901,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>171</v>
       </c>
@@ -2860,7 +2909,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>173</v>
       </c>
@@ -2868,7 +2917,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>175</v>
       </c>
@@ -2876,7 +2925,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>177</v>
       </c>
@@ -2884,7 +2933,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>179</v>
       </c>
@@ -2892,7 +2941,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>181</v>
       </c>
@@ -2900,7 +2949,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>183</v>
       </c>
@@ -2908,7 +2957,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>185</v>
       </c>
@@ -2916,7 +2965,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>187</v>
       </c>
@@ -2924,7 +2973,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>189</v>
       </c>
@@ -2932,7 +2981,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>191</v>
       </c>
@@ -2940,7 +2989,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>193</v>
       </c>
@@ -2948,7 +2997,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>195</v>
       </c>
@@ -2956,7 +3005,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>197</v>
       </c>
@@ -2964,7 +3013,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>199</v>
       </c>
@@ -2972,7 +3021,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>201</v>
       </c>
@@ -2980,7 +3029,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>203</v>
       </c>
@@ -2988,7 +3037,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>205</v>
       </c>
@@ -2996,7 +3045,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>207</v>
       </c>
@@ -3004,7 +3053,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>209</v>
       </c>
@@ -3012,7 +3061,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>211</v>
       </c>
@@ -3020,7 +3069,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>213</v>
       </c>
@@ -3028,7 +3077,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>215</v>
       </c>
@@ -3036,7 +3085,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>217</v>
       </c>
@@ -3044,7 +3093,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>219</v>
       </c>
@@ -3052,7 +3101,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>221</v>
       </c>
@@ -3060,7 +3109,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>223</v>
       </c>
@@ -3068,7 +3117,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>225</v>
       </c>
@@ -3076,7 +3125,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>227</v>
       </c>
@@ -3084,7 +3133,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>229</v>
       </c>
@@ -3092,7 +3141,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>231</v>
       </c>
@@ -3100,7 +3149,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>233</v>
       </c>
@@ -3108,7 +3157,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>235</v>
       </c>
@@ -3116,7 +3165,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>237</v>
       </c>
@@ -3124,7 +3173,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>239</v>
       </c>
@@ -3132,7 +3181,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>241</v>
       </c>
@@ -3140,7 +3189,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>243</v>
       </c>
@@ -3148,7 +3197,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>245</v>
       </c>
@@ -3156,7 +3205,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>247</v>
       </c>
@@ -3164,7 +3213,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>249</v>
       </c>
@@ -3172,7 +3221,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>251</v>
       </c>
@@ -3180,7 +3229,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>253</v>
       </c>
@@ -3188,7 +3237,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
         <v>255</v>
       </c>
@@ -3196,7 +3245,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>257</v>
       </c>
@@ -3204,7 +3253,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>259</v>
       </c>
@@ -3212,7 +3261,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>261</v>
       </c>
@@ -3220,7 +3269,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>263</v>
       </c>
@@ -3228,7 +3277,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>265</v>
       </c>
@@ -3236,7 +3285,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
         <v>267</v>
       </c>
@@ -3244,7 +3293,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>269</v>
       </c>
@@ -3252,7 +3301,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
         <v>271</v>
       </c>
@@ -3260,7 +3309,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>273</v>
       </c>
@@ -3268,7 +3317,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>275</v>
       </c>
@@ -3276,7 +3325,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>277</v>
       </c>
@@ -3284,7 +3333,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>279</v>
       </c>
@@ -3292,7 +3341,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
         <v>281</v>
       </c>
@@ -3300,7 +3349,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
         <v>283</v>
       </c>
@@ -3308,7 +3357,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>285</v>
       </c>
@@ -3316,7 +3365,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
         <v>287</v>
       </c>
@@ -3324,7 +3373,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>289</v>
       </c>
@@ -3332,7 +3381,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>291</v>
       </c>
@@ -3340,7 +3389,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>293</v>
       </c>
@@ -3348,7 +3397,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>295</v>
       </c>
@@ -3356,7 +3405,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>297</v>
       </c>
@@ -3364,7 +3413,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>299</v>
       </c>
@@ -3372,7 +3421,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>301</v>
       </c>
@@ -3380,7 +3429,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>303</v>
       </c>
@@ -3388,7 +3437,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
         <v>305</v>
       </c>
@@ -3396,7 +3445,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>307</v>
       </c>
@@ -3404,7 +3453,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>309</v>
       </c>
@@ -3412,7 +3461,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>311</v>
       </c>
@@ -3420,7 +3469,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>313</v>
       </c>
@@ -3428,7 +3477,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>315</v>
       </c>
@@ -3436,7 +3485,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>317</v>
       </c>
@@ -3444,7 +3493,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>319</v>
       </c>
@@ -3452,7 +3501,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
         <v>321</v>
       </c>
@@ -3460,7 +3509,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>323</v>
       </c>
@@ -3468,7 +3517,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
         <v>325</v>
       </c>
@@ -3476,7 +3525,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>327</v>
       </c>
@@ -3484,7 +3533,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>329</v>
       </c>
@@ -3492,7 +3541,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
         <v>331</v>
       </c>
@@ -3500,7 +3549,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>333</v>
       </c>
@@ -3508,7 +3557,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A168" s="7" t="s">
         <v>335</v>
       </c>
@@ -3516,7 +3565,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>337</v>
       </c>
@@ -3524,7 +3573,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
         <v>339</v>
       </c>
@@ -3532,7 +3581,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>341</v>
       </c>
@@ -3540,7 +3589,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
         <v>343</v>
       </c>
@@ -3548,7 +3597,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>345</v>
       </c>
@@ -3556,7 +3605,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
         <v>347</v>
       </c>
@@ -3564,7 +3613,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>349</v>
       </c>
@@ -3572,7 +3621,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>351</v>
       </c>
@@ -3580,7 +3629,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>353</v>
       </c>
@@ -3588,7 +3637,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
         <v>355</v>
       </c>
@@ -3596,7 +3645,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>357</v>
       </c>
@@ -3604,7 +3653,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A180" s="7" t="s">
         <v>359</v>
       </c>
@@ -3612,7 +3661,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>361</v>
       </c>
@@ -3620,7 +3669,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>363</v>
       </c>
@@ -3628,7 +3677,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>365</v>
       </c>
@@ -3636,7 +3685,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A184" s="7" t="s">
         <v>367</v>
       </c>
@@ -3644,7 +3693,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
         <v>369</v>
       </c>
@@ -3652,7 +3701,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
         <v>371</v>
       </c>
@@ -3660,7 +3709,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>373</v>
       </c>
@@ -3668,7 +3717,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A188" s="7" t="s">
         <v>375</v>
       </c>
@@ -3676,7 +3725,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A189" s="7" t="s">
         <v>377</v>
       </c>
@@ -3684,7 +3733,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A190" s="7" t="s">
         <v>379</v>
       </c>
@@ -3692,7 +3741,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A191" s="7" t="s">
         <v>381</v>
       </c>
@@ -3700,7 +3749,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A192" s="7" t="s">
         <v>383</v>
       </c>
@@ -3708,7 +3757,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
         <v>385</v>
       </c>
@@ -3716,7 +3765,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A194" s="7" t="s">
         <v>387</v>
       </c>
@@ -3724,7 +3773,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>389</v>
       </c>
@@ -3732,7 +3781,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A196" s="7" t="s">
         <v>391</v>
       </c>
@@ -3740,7 +3789,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
         <v>393</v>
       </c>
@@ -3748,7 +3797,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A198" s="7" t="s">
         <v>395</v>
       </c>
@@ -3756,7 +3805,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A199" s="7" t="s">
         <v>397</v>
       </c>
@@ -3764,7 +3813,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A200" s="7" t="s">
         <v>399</v>
       </c>
@@ -3772,7 +3821,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>401</v>
       </c>
@@ -3780,7 +3829,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A202" s="7" t="s">
         <v>403</v>
       </c>
@@ -3788,7 +3837,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A203" s="7" t="s">
         <v>405</v>
       </c>
@@ -3796,7 +3845,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A204" s="7" t="s">
         <v>407</v>
       </c>
@@ -3804,7 +3853,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
         <v>409</v>
       </c>
@@ -3812,7 +3861,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
         <v>411</v>
       </c>
@@ -3820,7 +3869,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
         <v>413</v>
       </c>
@@ -3828,7 +3877,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A208" s="7" t="s">
         <v>415</v>
       </c>
@@ -3836,7 +3885,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>417</v>
       </c>
@@ -3844,7 +3893,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A210" s="7" t="s">
         <v>419</v>
       </c>
@@ -3852,7 +3901,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
         <v>2</v>
       </c>
@@ -3860,7 +3909,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
         <v>422</v>
       </c>
@@ -3868,7 +3917,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A213" s="7" t="s">
         <v>424</v>
       </c>
@@ -3876,7 +3925,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A214" s="7" t="s">
         <v>426</v>
       </c>
@@ -3884,7 +3933,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A215" s="7" t="s">
         <v>428</v>
       </c>
@@ -3892,7 +3941,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A216" s="7" t="s">
         <v>430</v>
       </c>
@@ -3900,7 +3949,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A217" s="7" t="s">
         <v>432</v>
       </c>
@@ -3908,7 +3957,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A218" s="7" t="s">
         <v>434</v>
       </c>
@@ -3916,7 +3965,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>436</v>
       </c>
@@ -3924,7 +3973,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A220" s="7" t="s">
         <v>438</v>
       </c>
@@ -3932,7 +3981,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A221" s="7" t="s">
         <v>440</v>
       </c>
@@ -3940,7 +3989,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A222" s="7" t="s">
         <v>442</v>
       </c>
@@ -3948,7 +3997,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A223" s="7" t="s">
         <v>444</v>
       </c>
@@ -3956,7 +4005,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A224" s="7" t="s">
         <v>446</v>
       </c>
@@ -3964,7 +4013,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A225" s="7" t="s">
         <v>448</v>
       </c>
@@ -3972,7 +4021,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A226" s="7" t="s">
         <v>450</v>
       </c>
@@ -3980,7 +4029,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>452</v>
       </c>
@@ -3988,7 +4037,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A228" s="7" t="s">
         <v>454</v>
       </c>
@@ -3996,7 +4045,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A229" s="7" t="s">
         <v>456</v>
       </c>
@@ -4004,7 +4053,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A230" s="7" t="s">
         <v>458</v>
       </c>
@@ -4012,7 +4061,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
         <v>460</v>
       </c>
@@ -4020,7 +4069,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A232" s="7" t="s">
         <v>462</v>
       </c>
@@ -4028,7 +4077,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A233" s="7" t="s">
         <v>464</v>
       </c>
@@ -4036,7 +4085,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A234" s="7" t="s">
         <v>466</v>
       </c>
@@ -4044,7 +4093,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A235" s="7" t="s">
         <v>468</v>
       </c>
@@ -4052,7 +4101,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
         <v>470</v>
       </c>
@@ -4060,7 +4109,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A237" s="7" t="s">
         <v>472</v>
       </c>
@@ -4068,7 +4117,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
         <v>474</v>
       </c>
@@ -4076,7 +4125,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A239" s="7" t="s">
         <v>476</v>
       </c>
@@ -4084,7 +4133,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A240" s="7" t="s">
         <v>478</v>
       </c>
@@ -4092,7 +4141,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A241" s="7" t="s">
         <v>480</v>
       </c>
@@ -4100,7 +4149,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A242" s="7" t="s">
         <v>482</v>
       </c>
@@ -4108,7 +4157,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A243" s="7" t="s">
         <v>484</v>
       </c>
@@ -4116,7 +4165,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A244" s="7" t="s">
         <v>486</v>
       </c>
@@ -4124,7 +4173,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A245" s="7" t="s">
         <v>488</v>
       </c>
@@ -4132,7 +4181,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A246" s="7" t="s">
         <v>490</v>
       </c>
@@ -4140,7 +4189,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A247" s="7" t="s">
         <v>492</v>
       </c>
@@ -4148,7 +4197,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A248" s="7" t="s">
         <v>494</v>
       </c>
@@ -4156,7 +4205,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
         <v>496</v>
       </c>
@@ -4164,7 +4213,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="21" x14ac:dyDescent="0.35">
       <c r="A250" s="7" t="s">
         <v>498</v>
       </c>

--- a/krm/static/files/import_companies_en.xlsx
+++ b/krm/static/files/import_companies_en.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicolasfernandorodri\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onedrive-global.kpmg.com/personal/nicolasfernandorodri_kpmg_es/Documents/Desktop/krm-kpmg/krm/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0611F973-7EDC-4BCE-9B03-8AE891EFAC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0611F973-7EDC-4BCE-9B03-8AE891EFAC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C56BFF52-4CD6-4D8C-95B8-2783AC7B4D0D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="510">
   <si>
     <t>VAT</t>
   </si>
@@ -1572,24 +1572,6 @@
   </si>
   <si>
     <t>TYPE</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>A123456</t>
-  </si>
-  <si>
-    <t>TEST ADDRESS</t>
-  </si>
-  <si>
-    <t>01234</t>
-  </si>
-  <si>
-    <t>test@nomail.com</t>
-  </si>
-  <si>
-    <t>COMPANY</t>
   </si>
   <si>
     <t>STATE</t>
@@ -2134,7 +2116,7 @@
         <v>501</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>502</v>
@@ -2153,36 +2135,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>509</v>
-      </c>
+      <c r="E3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E4" s="3"/>
@@ -2192,9 +2146,6 @@
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{418A89E0-4983-4AA2-9B80-6AD0FFC398BB}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
